--- a/ipo-analysis/companies/sfc-environmental-technologies-ltd/SFC_ENVIRONMENTAL_TECHNO_02_Anchor_QIB.xlsx
+++ b/ipo-analysis/companies/sfc-environmental-technologies-ltd/SFC_ENVIRONMENTAL_TECHNO_02_Anchor_QIB.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -152,7 +153,7 @@
     <xf numFmtId="4" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,8 +161,8 @@
     <xf numFmtId="4" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -971,7 +972,9 @@
           <t>Final offer price</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n"/>
+      <c r="C7" s="11" t="n">
+        <v>330</v>
+      </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Rs/share</t>
@@ -984,7 +987,9 @@
           <t>Anchor allocation price</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n"/>
+      <c r="C8" s="11" t="n">
+        <v>330</v>
+      </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Rs/share</t>
@@ -1003,7 +1008,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>150</v>
+        <v>667.53</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -1277,7 +1282,9 @@
           <t>Anchor bid / pay-in date</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n"/>
+      <c r="C31" s="16" t="n">
+        <v>46321</v>
+      </c>
       <c r="D31" s="9" t="inlineStr"/>
       <c r="E31" s="10" t="inlineStr">
         <is>
@@ -1291,7 +1298,9 @@
           <t>Allotment date (basis of allotment)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="n"/>
+      <c r="C32" s="16" t="n">
+        <v>46325</v>
+      </c>
       <c r="D32" s="9" t="inlineStr"/>
       <c r="E32" s="10" t="inlineStr">
         <is>
@@ -1305,7 +1314,9 @@
           <t>Listing date</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n"/>
+      <c r="C33" s="16" t="n">
+        <v>46329</v>
+      </c>
       <c r="D33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
@@ -2386,7 +2397,9 @@
           <t>Total post-issue shares (lakh)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n"/>
+      <c r="C4" s="11" t="n">
+        <v>979.5599999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="18" t="inlineStr">
@@ -2536,11 +2549,11 @@
     <row r="11">
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Pre-issue non-promoter shareholders (other than OFS shares)</t>
+          <t>Pre-issue non-promoter shareholders (net of OFS)</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>388.16</v>
+        <v>374</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>180</v>
@@ -2567,7 +2580,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>pp. 31, 113; six months - confirm in RHP</t>
+          <t>pp. 29-30 (cover); six months</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2591,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>230.43</v>
+        <v>207.37</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>180</v>
@@ -2605,7 +2618,7 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>p. 31; six months (no capex object) - confirm in RHP</t>
+          <t>six months (no capex object)</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2629,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>192.45</v>
+        <v>195.91</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>540</v>
@@ -2643,7 +2656,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>18 months - confirm in RHP</t>
+          <t>18 months</t>
         </is>
       </c>
     </row>
